--- a/Ejercicio no tan simple de IRRBB.xlsx
+++ b/Ejercicio no tan simple de IRRBB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samue\OneDrive\Desktop\TRABAJO\UNI\8VO SEMESTRE\ADMINISTRACION_RIESGOS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBE0EA9E-20E2-40EE-8F41-31B119CABB45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FFE59A8-278E-4675-B827-02AC16846DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{637D9833-9F85-4F4B-A174-2A3F6A0823AC}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{637D9833-9F85-4F4B-A174-2A3F6A0823AC}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -651,14 +651,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0FB77BED-63EC-4B42-9DC4-1B20F8B6E96A}">
   <dimension ref="C5:L34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="3" width="21.77734375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.21875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="17.21875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="5" spans="3:9" x14ac:dyDescent="0.25">
       <c r="D5" s="1" t="s">
         <v>4</v>
       </c>
@@ -675,7 +675,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="6" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C6" t="s">
         <v>0</v>
       </c>
@@ -696,7 +696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="7" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C7" t="s">
         <v>1</v>
       </c>
@@ -717,7 +717,7 @@
         <v>-54.4</v>
       </c>
     </row>
-    <row r="8" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="8" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C8" t="s">
         <v>2</v>
       </c>
@@ -738,7 +738,7 @@
         <v>-0.96</v>
       </c>
     </row>
-    <row r="9" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="9" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C9" t="s">
         <v>3</v>
       </c>
@@ -759,7 +759,7 @@
         <v>-210</v>
       </c>
     </row>
-    <row r="10" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="10" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C10" s="4" t="s">
         <v>13</v>
       </c>
@@ -772,7 +772,7 @@
         <v>-265.36</v>
       </c>
     </row>
-    <row r="12" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="12" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C12" t="s">
         <v>17</v>
       </c>
@@ -793,7 +793,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="13" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
         <v>14</v>
       </c>
@@ -810,11 +810,11 @@
         <v>0.08</v>
       </c>
       <c r="I13">
-        <f t="shared" ref="I13:I15" si="1">-D13*G13*0.01</f>
+        <f>-D13*G13*0.01</f>
         <v>-1.2</v>
       </c>
     </row>
-    <row r="14" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C14" t="s">
         <v>15</v>
       </c>
@@ -831,11 +831,11 @@
         <v>0.08</v>
       </c>
       <c r="I14">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="I13:I15" si="1">-D14*G14*0.01</f>
         <v>-0.8</v>
       </c>
     </row>
-    <row r="15" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="15" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C15" t="s">
         <v>16</v>
       </c>
@@ -856,7 +856,7 @@
         <v>-108</v>
       </c>
     </row>
-    <row r="16" spans="3:9" x14ac:dyDescent="0.3">
+    <row r="16" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C16" t="s">
         <v>18</v>
       </c>
@@ -877,7 +877,7 @@
         <v>-110</v>
       </c>
     </row>
-    <row r="17" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C17" s="4" t="s">
         <v>21</v>
       </c>
@@ -890,12 +890,12 @@
         <v>-155.36000000000001</v>
       </c>
     </row>
-    <row r="19" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="19" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C19" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="20" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C20" s="6"/>
       <c r="D20" s="6" t="s">
         <v>25</v>
@@ -913,7 +913,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="21" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C21" s="6" t="s">
         <v>23</v>
       </c>
@@ -929,7 +929,7 @@
         <v>3300</v>
       </c>
     </row>
-    <row r="22" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="22" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C22" s="6" t="s">
         <v>24</v>
       </c>
@@ -945,7 +945,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="23" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="23" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C23" s="1" t="s">
         <v>30</v>
       </c>
@@ -958,22 +958,22 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="25" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="25" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C25" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="26" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="26" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C26" s="7" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="27" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="27" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>36</v>
       </c>
     </row>
-    <row r="30" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="30" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C30" s="8" t="s">
         <v>33</v>
       </c>
@@ -982,7 +982,7 @@
         <v>-13</v>
       </c>
     </row>
-    <row r="31" spans="3:12" x14ac:dyDescent="0.3">
+    <row r="31" spans="3:12" x14ac:dyDescent="0.25">
       <c r="C31" t="s">
         <v>34</v>
       </c>
@@ -991,7 +991,7 @@
         <v>-0.31072000000000005</v>
       </c>
     </row>
-    <row r="34" spans="3:3" x14ac:dyDescent="0.3">
+    <row r="34" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C34" t="s">
         <v>35</v>
       </c>
